--- a/dashboard_bienestar_docente.xlsx
+++ b/dashboard_bienestar_docente.xlsx
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6538</v>
+        <v>10634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44.6</v>
+        <v>72.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1234</v>
+        <v>2002</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>14.6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18309</v>
+        <v>26699</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>321843</v>
+        <v>473646</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1538</v>
+        <v>1764</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="E2" t="n">
-        <v>2634</v>
+        <v>3987</v>
       </c>
       <c r="F2" t="n">
-        <v>61162</v>
+        <v>83383</v>
       </c>
     </row>
     <row r="3">
@@ -1654,16 +1654,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>653</v>
+        <v>1552</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
-        <v>562</v>
+        <v>912</v>
       </c>
       <c r="F3" t="n">
-        <v>10047</v>
+        <v>16707</v>
       </c>
     </row>
     <row r="4">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VILLA EL SALVADOR</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>615</v>
+        <v>1087</v>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="E4" t="n">
-        <v>789</v>
+        <v>904</v>
       </c>
       <c r="F4" t="n">
-        <v>12946</v>
+        <v>13939</v>
       </c>
     </row>
     <row r="5">
@@ -1694,20 +1694,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>516</v>
+        <v>773</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>629</v>
+        <v>351</v>
       </c>
       <c r="F5" t="n">
-        <v>10324</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="6">
@@ -1716,20 +1716,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOS OLIVOS</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>447</v>
+        <v>755</v>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="E6" t="n">
-        <v>515</v>
+        <v>1176</v>
       </c>
       <c r="F6" t="n">
-        <v>9116</v>
+        <v>20014</v>
       </c>
     </row>
     <row r="7">
@@ -1738,20 +1738,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>504</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>476</v>
+        <v>770</v>
       </c>
       <c r="F7" t="n">
-        <v>8560</v>
+        <v>13119</v>
       </c>
     </row>
     <row r="8">
@@ -1760,20 +1760,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VENTANILLA</t>
+          <t>RIMAC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>229</v>
+        <v>384</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="F8" t="n">
-        <v>8059</v>
+        <v>6638</v>
       </c>
     </row>
     <row r="9">
@@ -1782,20 +1782,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA VICTORIA</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>381</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="E9" t="n">
-        <v>321</v>
+        <v>695</v>
       </c>
       <c r="F9" t="n">
-        <v>4389</v>
+        <v>12473</v>
       </c>
     </row>
     <row r="10">
@@ -1804,20 +1804,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RIMAC</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>199</v>
+        <v>341</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>319</v>
+        <v>682</v>
       </c>
       <c r="F10" t="n">
-        <v>5376</v>
+        <v>10204</v>
       </c>
     </row>
     <row r="11">
@@ -1826,20 +1826,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANTA ANITA</t>
+          <t>ATE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="E11" t="n">
-        <v>601</v>
+        <v>1418</v>
       </c>
       <c r="F11" t="n">
-        <v>9145</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="12">
@@ -1848,20 +1848,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA MOLINA</t>
+          <t>CHORRILLOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>271</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
-        <v>437</v>
+        <v>793</v>
       </c>
       <c r="F12" t="n">
-        <v>4438</v>
+        <v>14308</v>
       </c>
     </row>
     <row r="13">
@@ -1870,20 +1870,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>VENTANILLA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>129</v>
+        <v>245</v>
       </c>
       <c r="D13" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="E13" t="n">
-        <v>980</v>
+        <v>578</v>
       </c>
       <c r="F13" t="n">
-        <v>17131</v>
+        <v>10199</v>
       </c>
     </row>
     <row r="14">
@@ -1892,20 +1892,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATE</t>
+          <t>BREÑA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>127</v>
+        <v>212</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>830</v>
+        <v>245</v>
       </c>
       <c r="F14" t="n">
-        <v>14027</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="15">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHORRILLOS</t>
+          <t>CALLAO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="E15" t="n">
-        <v>560</v>
+        <v>1367</v>
       </c>
       <c r="F15" t="n">
-        <v>9589</v>
+        <v>23655</v>
       </c>
     </row>
     <row r="16">
@@ -1940,16 +1940,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="E16" t="n">
-        <v>675</v>
+        <v>967</v>
       </c>
       <c r="F16" t="n">
-        <v>10602</v>
+        <v>16020</v>
       </c>
     </row>
     <row r="17">
@@ -1962,16 +1962,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="D17" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="E17" t="n">
-        <v>898</v>
+        <v>1401</v>
       </c>
       <c r="F17" t="n">
-        <v>14748</v>
+        <v>24614</v>
       </c>
     </row>
     <row r="18">
@@ -1980,20 +1980,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIRAFLORES</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>187</v>
+        <v>440</v>
       </c>
       <c r="F18" t="n">
-        <v>2090</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="19">
@@ -2006,16 +2006,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="F19" t="n">
-        <v>3790</v>
+        <v>4806</v>
       </c>
     </row>
     <row r="20">
@@ -2024,20 +2024,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="E20" t="n">
-        <v>763</v>
+        <v>1214</v>
       </c>
       <c r="F20" t="n">
-        <v>11577</v>
+        <v>22783</v>
       </c>
     </row>
     <row r="21">
@@ -2046,20 +2046,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BREÑA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="E21" t="n">
-        <v>131</v>
+        <v>2129</v>
       </c>
       <c r="F21" t="n">
-        <v>1797</v>
+        <v>44056</v>
       </c>
     </row>
     <row r="22">
@@ -2068,20 +2068,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>LINCE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" t="n">
         <v>50</v>
       </c>
-      <c r="E22" t="n">
-        <v>747</v>
-      </c>
       <c r="F22" t="n">
-        <v>13651</v>
+        <v>666</v>
       </c>
     </row>
     <row r="23">
@@ -2090,20 +2090,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA PERLA</t>
+          <t>PUEBLO LIBRE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="F23" t="n">
-        <v>2935</v>
+        <v>859</v>
       </c>
     </row>
     <row r="24">
@@ -2112,20 +2112,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PUEBLO LIBRE</t>
+          <t>MIRAFLORES</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>221</v>
       </c>
       <c r="F24" t="n">
-        <v>826</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="25">
@@ -2134,20 +2134,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANTIAGO DE SURCO</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>469</v>
+        <v>148</v>
       </c>
       <c r="F25" t="n">
-        <v>5540</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="26">
@@ -2156,20 +2156,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAGDALENA DEL MAR</t>
+          <t>PACHACAMAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>323</v>
       </c>
       <c r="F26" t="n">
-        <v>2729</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="27">
@@ -2178,20 +2178,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CARABAYLLO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
-        <v>256</v>
+        <v>563</v>
       </c>
       <c r="F27" t="n">
-        <v>5134</v>
+        <v>7204</v>
       </c>
     </row>
     <row r="28">
@@ -2200,20 +2200,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LINCE</t>
+          <t>LA PERLA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>36</v>
+        <v>312</v>
       </c>
       <c r="F28" t="n">
-        <v>439</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="29">
@@ -2226,16 +2226,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E29" t="n">
-        <v>333</v>
+        <v>542</v>
       </c>
       <c r="F29" t="n">
-        <v>6783</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="30">
@@ -2244,20 +2244,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PACHACAMAC</t>
+          <t>CARABAYLLO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="F30" t="n">
-        <v>5929</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="31">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LURIGANCHO</t>
+          <t>MAGDALENA DEL MAR</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>393</v>
+        <v>303</v>
       </c>
       <c r="F31" t="n">
-        <v>7606</v>
+        <v>4308</v>
       </c>
     </row>
   </sheetData>
@@ -2385,7 +2385,7 @@
         <v>326</v>
       </c>
       <c r="H2" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="I2" t="n">
         <v>81</v>
@@ -2434,17 +2434,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>536412</t>
+          <t>605349</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HAPPY FACE</t>
+          <t>TECHNOLOGY SCHOOLS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Villa El Salvador</t>
+          <t>Puente Piedra</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2453,16 +2453,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="H4" t="n">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="I4" t="n">
-        <v>83.8</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="5">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>334447</t>
+          <t>536412</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
+          <t>HAPPY FACE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>San Martín de Porres</t>
+          <t>Villa El Salvador</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2496,10 +2496,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="I5" t="n">
-        <v>62.6</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="6">
@@ -2508,17 +2508,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>697607</t>
+          <t>334447</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JESUS ES MI GUIA</t>
+          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Los Olivos</t>
+          <t>San Martín de Porres</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="I6" t="n">
-        <v>97.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="7">
@@ -2545,17 +2545,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>346799</t>
+          <t>333419</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7217 OLIMPIA GERALDINA MELENDEZ PERALTA</t>
+          <t>3042 JESUS EL SALVADOR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Villa María del Triunfo</t>
+          <t>San Martín de Porres</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2567,13 +2567,13 @@
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>345</v>
+        <v>455</v>
       </c>
       <c r="H7" t="n">
-        <v>286</v>
+        <v>439</v>
       </c>
       <c r="I7" t="n">
-        <v>68.59999999999999</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="8">
@@ -2582,35 +2582,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>144777</t>
+          <t>697607</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5120 JOSE CARLOS MARIATEGUI LA CHIRA</t>
+          <t>JESUS ES MI GUIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ventanilla</t>
+          <t>Los Olivos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>404</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>187</v>
+        <v>394</v>
       </c>
       <c r="I8" t="n">
-        <v>80.7</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="9">
@@ -2619,35 +2619,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>703095</t>
+          <t>346799</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>7217 OLIMPIA GERALDINA MELENDEZ PERALTA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>La Victoria</t>
+          <t>Villa María del Triunfo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>86</v>
+        <v>345</v>
       </c>
       <c r="H9" t="n">
-        <v>185</v>
+        <v>286</v>
       </c>
       <c r="I9" t="n">
-        <v>66.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2656,35 +2656,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>321039</t>
+          <t>144777</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SEMILLITAS DEL SABER</t>
+          <t>5120 JOSE CARLOS MARIATEGUI LA CHIRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rímac</t>
+          <t>Ventanilla</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>404</v>
       </c>
       <c r="H10" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="I10" t="n">
-        <v>31.7</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="11">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>338718</t>
+          <t>113521</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>107 DANIEL ALCIDES CARRION GARCIA</t>
+          <t>SANTA ROSA VI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Santa Anita</t>
+          <t>La Victoria</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2712,16 +2712,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2563</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="I11" t="n">
-        <v>6.7</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="12">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>720472</t>
+          <t>309725</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HUMANITAS</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>La Molina</t>
+          <t>La Victoria</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2749,16 +2749,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>66</v>
+        <v>371</v>
       </c>
       <c r="H12" t="n">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="I12" t="n">
-        <v>99.5</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="13">
@@ -2767,35 +2767,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>108670</t>
+          <t>703095</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ANGELITOS DE JESUS B</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>San Juan de Lurigancho</t>
+          <t>La Victoria</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="H13" t="n">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="I13" t="n">
-        <v>27.5</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2804,35 +2804,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>317377</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MY FRIENDS</t>
+          <t>SANTA ROSA VIII</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Miraflores</t>
+          <t>La Victoria</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="I14" t="n">
-        <v>77.7</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>143301</t>
+          <t>321039</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PULGARCITO</t>
+          <t>SEMILLITAS DEL SABER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Rímac</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2860,16 +2860,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H15" t="n">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="I15" t="n">
-        <v>54.3</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="16">
@@ -2878,35 +2878,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>102338</t>
+          <t>320935</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AYNI-DAME TU MANO</t>
+          <t>NUESTRA SEÑORA DE LA CONSOLACION</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Villa El Salvador</t>
+          <t>Rímac</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>25</v>
+        <v>524</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="I16" t="n">
-        <v>64.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -2915,17 +2915,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>295592</t>
+          <t>338718</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1005 JORGE CHAVEZ DARTNELL</t>
+          <t>107 DANIEL ALCIDES CARRION GARCIA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Breña</t>
+          <t>Santa Anita</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>345</v>
+        <v>2563</v>
       </c>
       <c r="H17" t="n">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="I17" t="n">
-        <v>22.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="18">
@@ -2952,17 +2952,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>718110</t>
+          <t>721264</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LAS COLINAS DE SANTA ROSA</t>
+          <t>STAN MAKLAN COLLEGE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Callao</t>
+          <t>Ate</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2971,16 +2971,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H18" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="I18" t="n">
-        <v>55</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2989,35 +2989,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>118244</t>
+          <t>720472</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ENMANUEL</t>
+          <t>HUMANITAS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chorrillos</t>
+          <t>La Molina</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H19" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="I19" t="n">
-        <v>31.7</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="20">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>315340</t>
+          <t>108670</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>072 SAN MARTIN DE PORRES</t>
+          <t>ANGELITOS DE JESUS B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Magdalena Del Mar</t>
+          <t>San Juan de Lurigancho</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3045,16 +3045,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>623</v>
+        <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="I20" t="n">
-        <v>41.9</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="21">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>143730</t>
+          <t>107167</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JOSE OLAYA BALANDRA</t>
+          <t>ANGELITOS DE JESUS - C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>La Perla</t>
+          <t>San Juan de Lurigancho</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3082,16 +3082,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>670</v>
+        <v>16</v>
       </c>
       <c r="H21" t="n">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="I21" t="n">
-        <v>69.40000000000001</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="22">
@@ -3100,35 +3100,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>333419</t>
+          <t>317377</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3042 JESUS EL SALVADOR</t>
+          <t>MY FRIENDS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>San Martín de Porres</t>
+          <t>Miraflores</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>455</v>
+        <v>93</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="I22" t="n">
-        <v>43.1</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="23">
@@ -3137,35 +3137,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>720165</t>
+          <t>867874</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1236 ALFONSO BARRANTES LINGAN</t>
+          <t>PAULO VI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ate</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1447</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="I23" t="n">
-        <v>78.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -3174,17 +3174,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>804141</t>
+          <t>143301</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BRITISH INTERNATIONAL SCHOOL</t>
+          <t>PULGARCITO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pueblo Libre</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3193,16 +3193,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="H24" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="I24" t="n">
-        <v>70.7</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="25">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>107903</t>
+          <t>102446</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SEMBRADOR</t>
+          <t>MISKI PURIY-DULCE CAMINAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ate</t>
+          <t>Villa El Salvador</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3233,13 +3233,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H25" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="I25" t="n">
-        <v>82.8</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3248,35 +3248,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>916577</t>
+          <t>102338</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BRITISH INTERNATIONAL SCHOOL</t>
+          <t>AYNI-DAME TU MANO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Magdalena Del Mar</t>
+          <t>Villa El Salvador</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="I26" t="n">
-        <v>70.7</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3285,17 +3285,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>346822</t>
+          <t>295610</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>1008 VIRGEN DE LOURDES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Villa María del Triunfo</t>
+          <t>Breña</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3304,16 +3304,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>760</v>
+        <v>358</v>
       </c>
       <c r="H27" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="I27" t="n">
-        <v>96.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>296964</t>
+          <t>295592</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2050 REPUBLICA DE ARGENTINA</t>
+          <t>1005 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Carabayllo</t>
+          <t>Breña</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3341,16 +3341,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>1648</v>
+        <v>345</v>
       </c>
       <c r="H28" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="I28" t="n">
-        <v>58.3</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="29">
@@ -3359,35 +3359,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>720387</t>
+          <t>295733</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA</t>
+          <t>1014 REP. ORIENTAL DEL URUGUAY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ate</t>
+          <t>Breña</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>2135</v>
+        <v>336</v>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I29" t="n">
-        <v>19.2</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="30">
@@ -3396,35 +3396,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>747631</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LUCERITOS</t>
+          <t>GOTTFRIED WILHELM LEIBNIZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Chorrillos</t>
+          <t>Breña</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I30" t="n">
-        <v>89.2</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="31">
@@ -3433,35 +3433,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>104883</t>
+          <t>718110</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NUEVO MUNDO 5</t>
+          <t>LAS COLINAS DE SANTA ROSA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Santiago de Surco</t>
+          <t>Callao</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I31" t="n">
-        <v>92.3</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3634,7 +3634,7 @@
         <v>7587</v>
       </c>
       <c r="C2" t="n">
-        <v>856</v>
+        <v>1321</v>
       </c>
       <c r="D2" t="n">
         <v>91870</v>
@@ -3643,7 +3643,7 @@
         <v>1350101</v>
       </c>
       <c r="F2" t="n">
-        <v>11.3</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="3">
@@ -3656,7 +3656,7 @@
         <v>6038</v>
       </c>
       <c r="C3" t="n">
-        <v>367</v>
+        <v>666</v>
       </c>
       <c r="D3" t="n">
         <v>76440</v>
@@ -3665,7 +3665,7 @@
         <v>1511351</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3678,7 +3678,7 @@
         <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>3838</v>
@@ -3687,7 +3687,7 @@
         <v>76895</v>
       </c>
       <c r="F4" t="n">
-        <v>9.800000000000001</v>
+        <v>13.4</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_bienestar_docente.xlsx
+++ b/dashboard_bienestar_docente.xlsx
@@ -2298,13 +2298,13 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2385,10 +2385,10 @@
         <v>1447</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>84.8</v>
+        <v>84.77590289557121</v>
       </c>
     </row>
     <row r="3">
@@ -2397,35 +2397,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>292555</t>
+          <t>856314</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>162 ANGELITOS DE JESUS</t>
+          <t>MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ate</t>
+          <t>Santa Anita</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>312</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>61.3</v>
+        <v>33.34392620793995</v>
       </c>
     </row>
     <row r="4">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>720448</t>
+          <t>235051</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIÑO DIOS</t>
+          <t>PEDACITO DE CIELO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2453,16 +2453,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>71.5</v>
+        <v>24.55155601797208</v>
       </c>
     </row>
     <row r="5">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>856314</t>
+          <t>336385</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MONITOR HUASCAR</t>
+          <t>ANDRES RAZURI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Santa Anita</t>
+          <t>San Martín de Porres</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>121</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>86</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
       <c r="I5" t="n">
-        <v>33.3</v>
+        <v>59.27249575084621</v>
       </c>
     </row>
     <row r="6">
@@ -2508,17 +2508,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>235051</t>
+          <t>142274</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PEDACITO DE CIELO</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Santa Anita</t>
+          <t>Callao</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>24.6</v>
+        <v>29.20091940919988</v>
       </c>
     </row>
     <row r="7">
@@ -2570,10 +2570,10 @@
         <v>67</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>2.394751068039707</v>
       </c>
     </row>
     <row r="8">
@@ -2582,17 +2582,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>581616</t>
+          <t>300112</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN VICENTE PALLOTI</t>
+          <t>SANTISIMA TRINIDAD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Callao</t>
+          <t>Chorrillos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>69.3</v>
+        <v>76.4272893763913</v>
       </c>
     </row>
     <row r="9">
@@ -2619,35 +2619,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>142274</t>
+          <t>338718</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>107 DANIEL ALCIDES CARRION GARCIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Callao</t>
+          <t>Santa Anita</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>151</v>
+        <v>2563</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>29.2</v>
+        <v>6.681522836670685</v>
       </c>
     </row>
     <row r="10">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>336385</t>
+          <t>319512</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANDRES RAZURI</t>
+          <t>MI NUEVO MUNDO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>San Martín de Porres</t>
+          <t>Puente Piedra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>59.3</v>
+        <v>38.49355275977558</v>
       </c>
     </row>
     <row r="11">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>304501</t>
+          <t>554123</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JACK GOLDFARB</t>
+          <t>RAYITOS DE CLARIDAD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Comas</t>
+          <t>Santa Anita</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2712,16 +2712,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>250</v>
+        <v>24</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>31.5</v>
+        <v>47.52245433730629</v>
       </c>
     </row>
     <row r="12">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>233349</t>
+          <t>319833</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SEÑOR DE LUREN</t>
+          <t>SANTA MARIA REYNA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Comas</t>
+          <t>Puente Piedra</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2749,16 +2749,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>81.59999999999999</v>
+        <v>47.76366102527987</v>
       </c>
     </row>
     <row r="13">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>305586</t>
+          <t>143198</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MARIA DE LOS ANGELES</t>
+          <t>MAX GUNTHER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>El Agustino</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2786,16 +2786,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>43</v>
+        <v>262</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>39.6757928440102</v>
       </c>
     </row>
     <row r="14">
@@ -2804,35 +2804,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>566036</t>
+          <t>320836</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES</t>
+          <t>3075 PATRICIA FRANCISCA SILVA DE PAGADOR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>San Juan de Lurigancho</t>
+          <t>Rímac</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>262</v>
+        <v>388</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.02762983114967</v>
       </c>
     </row>
     <row r="15">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>104808</t>
+          <t>323887</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PEDACITO DE CIELO 1</t>
+          <t>0062</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Juan de Lurigancho</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2860,16 +2860,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>365</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>65.90000000000001</v>
+        <v>38.93259951916189</v>
       </c>
     </row>
     <row r="16">
@@ -2878,17 +2878,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>549462</t>
+          <t>537157</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SOR MARIA FAUSTINA KOWALSKA</t>
+          <t>HAPPY DAYS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Juan de Lurigancho</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2897,16 +2897,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>60</v>
+        <v>45.59451925095894</v>
       </c>
     </row>
     <row r="17">
@@ -2915,17 +2915,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>710543</t>
+          <t>755800</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAVIA ESTUDIANTIL</t>
+          <t>SEMILLITAS DE STANFORD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Comas</t>
+          <t>San Martín de Porres</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2937,13 +2937,13 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>40.6</v>
+        <v>56.33796169919697</v>
       </c>
     </row>
     <row r="18">
@@ -2952,17 +2952,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>537157</t>
+          <t>602732</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HAPPY DAYS</t>
+          <t>LOS ALAMITOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>San Juan de Lurigancho</t>
+          <t>Rímac</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2971,16 +2971,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>45.6</v>
+        <v>47.73262739840425</v>
       </c>
     </row>
     <row r="19">
@@ -2989,17 +2989,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>554123</t>
+          <t>725790</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RAYITOS DE CLARIDAD</t>
+          <t>LITTLE HANDS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Santa Anita</t>
+          <t>Chorrillos</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3008,16 +3008,16 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="n">
-        <v>24</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
       <c r="I19" t="n">
-        <v>47.5</v>
+        <v>18.47947857656327</v>
       </c>
     </row>
     <row r="20">
@@ -3026,35 +3026,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>326503</t>
+          <t>304978</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES</t>
+          <t>1046 JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>San Juan de Lurigancho</t>
+          <t>El Agustino</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>348</v>
+        <v>185</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>36.2</v>
+        <v>57.76599430373338</v>
       </c>
     </row>
     <row r="21">
@@ -3063,35 +3063,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>715687</t>
+          <t>139969</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JUAN RULFO</t>
+          <t>5005 GENMO DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>San Juan de Lurigancho</t>
+          <t>Callao</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública de gestión directa</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>164</v>
+        <v>727</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>69.8</v>
+        <v>43.82798192919432</v>
       </c>
     </row>
     <row r="22">
@@ -3100,35 +3100,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>332207</t>
+          <t>839758</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1216 MIGUEL GRAU SEMINARIO</t>
+          <t>PERUANO DE SISTEMAS SISE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>929</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>42.3</v>
+        <v>73.26014451069477</v>
       </c>
     </row>
     <row r="23">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>326188</t>
+          <t>839744</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MATER PURISSIMA</t>
+          <t>PERUANO DE SISTEMAS SISE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>San Juan de Lurigancho</t>
+          <t>Puente Piedra</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3156,16 +3156,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>81</v>
+        <v>65.50464975882048</v>
       </c>
     </row>
     <row r="24">
@@ -3174,17 +3174,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>318598</t>
+          <t>604199</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ERICH KRAMM</t>
+          <t>LIBERTADOR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pucusana</t>
+          <t>Chorrillos</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3193,16 +3193,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>83</v>
+        <v>31.5313928007697</v>
       </c>
     </row>
     <row r="25">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>319512</t>
+          <t>140487</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MI NUEVO MUNDO</t>
+          <t>JOSE GALVEZ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Puente Piedra</t>
+          <t>Callao</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>178</v>
+        <v>361</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.5</v>
+        <v>67.59109353454899</v>
       </c>
     </row>
     <row r="26">
@@ -3248,35 +3248,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>113125</t>
+          <t>555981</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIS PRIMEROS PASOS 3</t>
+          <t>KUSILLARY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Pueblo Libre</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>79</v>
+        <v>31.75657307211591</v>
       </c>
     </row>
     <row r="27">
@@ -3285,35 +3285,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>112836</t>
+          <t>838513</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RAYITOS DE SOL 3</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Juan de Lurigancho</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>286</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>81.5</v>
+        <v>38.0888800266011</v>
       </c>
     </row>
     <row r="28">
@@ -3322,35 +3322,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>112815</t>
+          <t>566036</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MIS PRIMEROS PASOS 4</t>
+          <t>MARISCAL CACERES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Juan de Lurigancho</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>11</v>
+        <v>262</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>79.8</v>
+        <v>62.32075058007914</v>
       </c>
     </row>
     <row r="29">
@@ -3359,35 +3359,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>323887</t>
+          <t>681951</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0062</t>
+          <t>CENTRO DE INVESTIGACION Y CAPACITACION TECNOLOGICA - CICAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>San Juan de Lurigancho</t>
+          <t>Carabayllo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pública de gestión directa</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>38.9</v>
+        <v>20.71798544945018</v>
       </c>
     </row>
     <row r="30">
@@ -3396,17 +3396,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>602732</t>
+          <t>141175</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LOS ALAMITOS</t>
+          <t>VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rímac</t>
+          <t>Callao</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3415,16 +3415,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>28</v>
+        <v>265</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>47.7</v>
+        <v>54.44518262278372</v>
       </c>
     </row>
     <row r="31">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>319833</t>
+          <t>838443</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SANTA MARIA REYNA DE LOS ANGELES</t>
+          <t>CIBERTEC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Puente Piedra</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3452,16 +3452,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>47.8</v>
+        <v>73.26014451069477</v>
       </c>
     </row>
   </sheetData>
